--- a/internal_doc/05.测试设计/story/Sequence&AutoIncrement/参数校验.xlsx
+++ b/internal_doc/05.测试设计/story/Sequence&AutoIncrement/参数校验.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="34">
   <si>
     <t>name</t>
   </si>
@@ -179,6 +179,17 @@
 2.合法值时修改成功，自增字段属性正确。非法值时修改失败，错误信息正确
 3.修改失败，错误信息正确
 4.记录插入成功，自增字段值正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxValue字段参数校验</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.不设置
+2.设置为Int32/Long类型，覆盖：非法值：正边界外的值、负边界外的值、小于/等于MinValue；合法值：典型值、负边界值、正边界值、小于MinValue
+3.设置为其他类型，如浮点型、decimal类型等
+4.插入记录</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -325,8 +336,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I10" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
-  <autoFilter ref="A1:I10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I11" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
+  <autoFilter ref="A1:I11"/>
   <tableColumns count="9">
     <tableColumn id="1" uniqueName="name" name="name" dataDxfId="8">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/@name" xmlDataType="string"/>
@@ -645,7 +656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="38.25" style="1" customWidth="1"/>
@@ -793,7 +804,7 @@
     </row>
     <row r="6" spans="1:9" ht="81">
       <c r="A6" s="1" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>12</v>
@@ -808,7 +819,7 @@
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>14</v>
@@ -819,7 +830,7 @@
     </row>
     <row r="7" spans="1:9" ht="81">
       <c r="A7" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>12</v>
@@ -844,11 +855,10 @@
       </c>
     </row>
     <row r="8" spans="1:9" ht="81">
-      <c r="A8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="2" t="s">
+      <c r="A8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D8" s="1">
@@ -860,10 +870,10 @@
       <c r="F8" s="1">
         <v>1</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="2" t="s">
+      <c r="G8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I8" s="1">
@@ -872,7 +882,7 @@
     </row>
     <row r="9" spans="1:9" ht="81">
       <c r="A9" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="2" t="s">
@@ -888,7 +898,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>14</v>
@@ -897,30 +907,57 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="67.5">
+    <row r="10" spans="1:9" ht="81">
       <c r="A10" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="1">
+        <v>2</v>
+      </c>
+      <c r="E10" s="1">
+        <v>2</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="67.5">
+      <c r="A11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="1">
-        <v>2</v>
-      </c>
-      <c r="E10" s="1">
-        <v>2</v>
-      </c>
-      <c r="F10" s="1">
-        <v>1</v>
-      </c>
-      <c r="G10" s="2" t="s">
+      <c r="D11" s="1">
+        <v>2</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="I10" s="1">
+      <c r="I11" s="1">
         <v>2</v>
       </c>
     </row>

--- a/internal_doc/05.测试设计/story/Sequence&AutoIncrement/参数校验.xlsx
+++ b/internal_doc/05.测试设计/story/Sequence&AutoIncrement/参数校验.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="35">
   <si>
     <t>name</t>
   </si>
@@ -190,6 +190,13 @@
 2.设置为Int32/Long类型，覆盖：非法值：正边界外的值、负边界外的值、小于/等于MinValue；合法值：典型值、负边界值、正边界值、小于MinValue
 3.设置为其他类型，如浮点型、decimal类型等
 4.插入记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.创建成功，默认值正确
+2.合法值时创建成功，自增字段属性正确。非法值时创建失败，错误信息正确
+3.创建失败，错误信息正确
+4.记录插入成功，自增字段值正确</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -822,7 +829,7 @@
         <v>33</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="I6" s="1">
         <v>2</v>
